--- a/데이터/opened_course2025_2.xlsx
+++ b/데이터/opened_course2025_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d90a49386c3f612/바탕 화면/AI융개_팀플/데이터/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{96D94FC5-E95A-4D19-AC32-E37E6C23D71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF513D4-E6EE-49AC-8F9D-2052BA484D77}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070B0A6A-F6F0-433E-B146-D8ACAF39E279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="심화전공2025_2" sheetId="5" r:id="rId1"/>
@@ -20,12 +20,11 @@
     <sheet name="공통교양2025_2" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="940">
   <si>
     <t>수리통계데이터사이언스학부</t>
   </si>
@@ -2258,10 +2257,6 @@
   </si>
   <si>
     <t>[1학년전공탐색] [GeM(SW문해)] 융합보안공학과 주/부/복수전공/창의융합학부 수강가능</t>
-  </si>
-  <si>
-    <t>이구수분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>핵심전공</t>
@@ -3427,16 +3422,16 @@
         <v>667</v>
       </c>
       <c r="B2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C2" t="s">
+        <v>865</v>
+      </c>
+      <c r="D2" t="s">
+        <v>939</v>
+      </c>
+      <c r="E2" t="s">
         <v>863</v>
-      </c>
-      <c r="C2" t="s">
-        <v>866</v>
-      </c>
-      <c r="D2" t="s">
-        <v>940</v>
-      </c>
-      <c r="E2" t="s">
-        <v>864</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -3459,16 +3454,16 @@
         <v>667</v>
       </c>
       <c r="B3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -3491,16 +3486,16 @@
         <v>667</v>
       </c>
       <c r="B4" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E4" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3523,16 +3518,16 @@
         <v>667</v>
       </c>
       <c r="B5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E5" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -3555,16 +3550,16 @@
         <v>667</v>
       </c>
       <c r="B6" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D6" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3587,16 +3582,16 @@
         <v>667</v>
       </c>
       <c r="B7" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C7" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E7" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -3619,16 +3614,16 @@
         <v>667</v>
       </c>
       <c r="B8" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C8" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E8" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -3651,16 +3646,16 @@
         <v>667</v>
       </c>
       <c r="B9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C9" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D9" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E9" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -3683,16 +3678,16 @@
         <v>667</v>
       </c>
       <c r="B10" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C10" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D10" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E10" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -3715,16 +3710,16 @@
         <v>667</v>
       </c>
       <c r="B11" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D11" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E11" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -3747,16 +3742,16 @@
         <v>667</v>
       </c>
       <c r="B12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C12" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D12" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -3779,16 +3774,16 @@
         <v>667</v>
       </c>
       <c r="B13" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C13" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D13" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -3803,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
@@ -3811,16 +3806,16 @@
         <v>663</v>
       </c>
       <c r="B14" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D14" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -3843,16 +3838,16 @@
         <v>663</v>
       </c>
       <c r="B15" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C15" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D15" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E15" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -3875,16 +3870,16 @@
         <v>663</v>
       </c>
       <c r="B16" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C16" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D16" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E16" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -3907,16 +3902,16 @@
         <v>663</v>
       </c>
       <c r="B17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C17" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D17" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E17" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -3939,16 +3934,16 @@
         <v>663</v>
       </c>
       <c r="B18" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C18" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D18" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E18" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F18">
         <v>3</v>
@@ -3971,16 +3966,16 @@
         <v>663</v>
       </c>
       <c r="B19" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C19" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D19" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E19" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -4003,16 +3998,16 @@
         <v>663</v>
       </c>
       <c r="B20" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C20" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D20" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E20" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -4035,16 +4030,16 @@
         <v>663</v>
       </c>
       <c r="B21" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C21" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D21" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E21" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F21">
         <v>3</v>
@@ -4067,16 +4062,16 @@
         <v>663</v>
       </c>
       <c r="B22" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C22" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D22" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E22" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F22">
         <v>3</v>
@@ -4099,16 +4094,16 @@
         <v>663</v>
       </c>
       <c r="B23" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C23" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D23" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E23" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -4131,16 +4126,16 @@
         <v>663</v>
       </c>
       <c r="B24" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C24" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D24" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E24" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -4163,16 +4158,16 @@
         <v>663</v>
       </c>
       <c r="B25" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C25" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D25" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E25" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -4195,16 +4190,16 @@
         <v>663</v>
       </c>
       <c r="B26" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C26" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D26" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E26" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F26">
         <v>3</v>
@@ -4227,16 +4222,16 @@
         <v>663</v>
       </c>
       <c r="B27" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C27" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D27" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E27" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -4259,16 +4254,16 @@
         <v>663</v>
       </c>
       <c r="B28" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C28" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D28" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E28" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -4291,16 +4286,16 @@
         <v>663</v>
       </c>
       <c r="B29" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C29" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D29" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E29" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F29">
         <v>3</v>
@@ -4323,16 +4318,16 @@
         <v>663</v>
       </c>
       <c r="B30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C30" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D30" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E30" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F30">
         <v>3</v>
@@ -4355,16 +4350,16 @@
         <v>663</v>
       </c>
       <c r="B31" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C31" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D31" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E31" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -4387,16 +4382,16 @@
         <v>655</v>
       </c>
       <c r="B32" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C32" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D32" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E32" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -4419,16 +4414,16 @@
         <v>655</v>
       </c>
       <c r="B33" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C33" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D33" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E33" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F33">
         <v>3</v>
@@ -4451,16 +4446,16 @@
         <v>655</v>
       </c>
       <c r="B34" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C34" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D34" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E34" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F34">
         <v>3</v>
@@ -4483,16 +4478,16 @@
         <v>655</v>
       </c>
       <c r="B35" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C35" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D35" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E35" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -4507,7 +4502,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
@@ -4515,16 +4510,16 @@
         <v>655</v>
       </c>
       <c r="B36" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C36" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D36" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E36" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F36">
         <v>3</v>
@@ -4539,7 +4534,7 @@
         <v>7</v>
       </c>
       <c r="J36" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
@@ -4547,16 +4542,16 @@
         <v>655</v>
       </c>
       <c r="B37" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C37" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D37" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E37" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F37">
         <v>3</v>
@@ -4579,16 +4574,16 @@
         <v>655</v>
       </c>
       <c r="B38" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C38" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D38" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E38" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -4611,16 +4606,16 @@
         <v>655</v>
       </c>
       <c r="B39" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C39" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D39" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E39" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -4643,16 +4638,16 @@
         <v>655</v>
       </c>
       <c r="B40" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C40" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D40" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E40" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -4675,16 +4670,16 @@
         <v>655</v>
       </c>
       <c r="B41" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C41" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D41" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E41" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -4699,7 +4694,7 @@
         <v>7</v>
       </c>
       <c r="J41" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
@@ -4707,16 +4702,16 @@
         <v>642</v>
       </c>
       <c r="B42" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C42" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D42" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E42" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F42">
         <v>3</v>
@@ -4739,16 +4734,16 @@
         <v>642</v>
       </c>
       <c r="B43" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C43" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D43" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E43" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F43">
         <v>3</v>
@@ -4771,16 +4766,16 @@
         <v>642</v>
       </c>
       <c r="B44" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C44" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D44" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E44" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F44">
         <v>3</v>
@@ -4803,16 +4798,16 @@
         <v>642</v>
       </c>
       <c r="B45" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C45" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D45" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E45" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -4835,16 +4830,16 @@
         <v>642</v>
       </c>
       <c r="B46" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C46" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D46" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E46" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F46">
         <v>2</v>
@@ -4867,16 +4862,16 @@
         <v>642</v>
       </c>
       <c r="B47" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C47" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D47" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E47" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -4899,16 +4894,16 @@
         <v>642</v>
       </c>
       <c r="B48" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C48" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D48" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E48" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F48">
         <v>3</v>
@@ -4923,7 +4918,7 @@
         <v>36</v>
       </c>
       <c r="J48" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
@@ -4931,16 +4926,16 @@
         <v>642</v>
       </c>
       <c r="B49" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C49" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D49" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E49" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -4963,16 +4958,16 @@
         <v>642</v>
       </c>
       <c r="B50" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C50" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D50" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E50" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F50">
         <v>3</v>
@@ -4995,16 +4990,16 @@
         <v>642</v>
       </c>
       <c r="B51" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C51" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D51" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E51" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F51">
         <v>3</v>
@@ -5027,16 +5022,16 @@
         <v>628</v>
       </c>
       <c r="B52" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C52" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D52" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E52" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F52">
         <v>3</v>
@@ -5059,16 +5054,16 @@
         <v>628</v>
       </c>
       <c r="B53" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C53" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D53" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E53" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F53">
         <v>2</v>
@@ -5091,16 +5086,16 @@
         <v>628</v>
       </c>
       <c r="B54" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C54" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D54" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E54" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F54">
         <v>3</v>
@@ -5123,16 +5118,16 @@
         <v>628</v>
       </c>
       <c r="B55" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C55" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D55" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E55" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F55">
         <v>2</v>
@@ -5155,16 +5150,16 @@
         <v>628</v>
       </c>
       <c r="B56" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C56" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D56" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E56" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F56">
         <v>3</v>
@@ -5187,16 +5182,16 @@
         <v>628</v>
       </c>
       <c r="B57" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C57" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D57" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E57" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F57">
         <v>3</v>
@@ -5211,7 +5206,7 @@
         <v>7</v>
       </c>
       <c r="J57" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
@@ -5219,16 +5214,16 @@
         <v>628</v>
       </c>
       <c r="B58" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C58" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D58" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E58" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F58">
         <v>3</v>
@@ -5251,16 +5246,16 @@
         <v>628</v>
       </c>
       <c r="B59" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C59" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D59" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E59" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -5275,7 +5270,7 @@
         <v>36</v>
       </c>
       <c r="J59" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
@@ -5283,16 +5278,16 @@
         <v>628</v>
       </c>
       <c r="B60" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C60" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D60" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E60" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F60">
         <v>3</v>
@@ -5307,7 +5302,7 @@
         <v>7</v>
       </c>
       <c r="J60" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
@@ -5315,16 +5310,16 @@
         <v>628</v>
       </c>
       <c r="B61" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C61" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D61" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E61" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F61">
         <v>2</v>
@@ -5339,7 +5334,7 @@
         <v>7</v>
       </c>
       <c r="J61" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
@@ -5347,16 +5342,16 @@
         <v>354</v>
       </c>
       <c r="B62" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C62" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D62" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E62" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F62">
         <v>2</v>
@@ -5371,7 +5366,7 @@
         <v>7</v>
       </c>
       <c r="J62" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
@@ -5379,16 +5374,16 @@
         <v>354</v>
       </c>
       <c r="B63" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C63" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D63" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E63" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F63">
         <v>2</v>
@@ -5403,7 +5398,7 @@
         <v>7</v>
       </c>
       <c r="J63" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
@@ -5411,16 +5406,16 @@
         <v>354</v>
       </c>
       <c r="B64" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C64" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D64" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E64" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F64">
         <v>3</v>
@@ -5435,7 +5430,7 @@
         <v>7</v>
       </c>
       <c r="J64" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
@@ -5443,16 +5438,16 @@
         <v>354</v>
       </c>
       <c r="B65" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C65" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D65" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E65" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F65">
         <v>3</v>
@@ -5475,16 +5470,16 @@
         <v>354</v>
       </c>
       <c r="B66" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C66" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D66" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E66" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F66">
         <v>3</v>
@@ -5507,16 +5502,16 @@
         <v>354</v>
       </c>
       <c r="B67" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C67" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D67" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E67" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -5539,16 +5534,16 @@
         <v>354</v>
       </c>
       <c r="B68" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C68" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D68" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E68" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F68">
         <v>3</v>
@@ -5571,16 +5566,16 @@
         <v>354</v>
       </c>
       <c r="B69" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C69" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D69" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E69" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F69">
         <v>3</v>
@@ -5595,7 +5590,7 @@
         <v>7</v>
       </c>
       <c r="J69" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
@@ -5603,16 +5598,16 @@
         <v>354</v>
       </c>
       <c r="B70" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C70" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D70" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E70" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -5627,7 +5622,7 @@
         <v>36</v>
       </c>
       <c r="J70" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
@@ -5635,16 +5630,16 @@
         <v>608</v>
       </c>
       <c r="B71" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C71" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D71" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E71" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F71">
         <v>3</v>
@@ -5667,16 +5662,16 @@
         <v>608</v>
       </c>
       <c r="B72" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C72" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D72" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E72" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F72">
         <v>3</v>
@@ -5691,7 +5686,7 @@
         <v>7</v>
       </c>
       <c r="J72" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
@@ -5699,16 +5694,16 @@
         <v>608</v>
       </c>
       <c r="B73" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C73" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D73" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E73" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F73">
         <v>2</v>
@@ -5731,16 +5726,16 @@
         <v>608</v>
       </c>
       <c r="B74" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C74" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D74" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E74" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F74">
         <v>3</v>
@@ -5755,7 +5750,7 @@
         <v>7</v>
       </c>
       <c r="J74" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
@@ -5763,16 +5758,16 @@
         <v>608</v>
       </c>
       <c r="B75" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C75" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D75" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E75" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F75">
         <v>3</v>
@@ -5787,7 +5782,7 @@
         <v>7</v>
       </c>
       <c r="J75" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
@@ -5795,16 +5790,16 @@
         <v>608</v>
       </c>
       <c r="B76" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C76" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D76" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E76" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F76">
         <v>3</v>
@@ -5819,7 +5814,7 @@
         <v>56</v>
       </c>
       <c r="J76" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
@@ -5827,16 +5822,16 @@
         <v>608</v>
       </c>
       <c r="B77" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C77" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D77" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E77" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F77">
         <v>3</v>
@@ -5859,16 +5854,16 @@
         <v>597</v>
       </c>
       <c r="B78" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C78" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D78" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E78" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F78">
         <v>3</v>
@@ -5883,7 +5878,7 @@
         <v>7</v>
       </c>
       <c r="J78" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
@@ -5891,16 +5886,16 @@
         <v>597</v>
       </c>
       <c r="B79" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C79" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D79" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E79" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F79">
         <v>3</v>
@@ -5915,7 +5910,7 @@
         <v>7</v>
       </c>
       <c r="J79" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
@@ -5923,16 +5918,16 @@
         <v>597</v>
       </c>
       <c r="B80" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C80" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D80" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E80" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F80">
         <v>3</v>
@@ -5947,7 +5942,7 @@
         <v>7</v>
       </c>
       <c r="J80" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
@@ -5955,16 +5950,16 @@
         <v>597</v>
       </c>
       <c r="B81" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C81" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D81" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E81" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F81">
         <v>3</v>
@@ -5979,7 +5974,7 @@
         <v>7</v>
       </c>
       <c r="J81" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
@@ -5987,16 +5982,16 @@
         <v>597</v>
       </c>
       <c r="B82" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C82" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D82" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E82" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F82">
         <v>3</v>
@@ -6011,7 +6006,7 @@
         <v>7</v>
       </c>
       <c r="J82" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
@@ -6019,16 +6014,16 @@
         <v>597</v>
       </c>
       <c r="B83" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C83" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D83" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E83" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F83">
         <v>3</v>
@@ -6043,7 +6038,7 @@
         <v>7</v>
       </c>
       <c r="J83" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
@@ -6051,16 +6046,16 @@
         <v>594</v>
       </c>
       <c r="B84" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C84" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D84" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E84" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F84">
         <v>3</v>
@@ -6075,7 +6070,7 @@
         <v>36</v>
       </c>
       <c r="J84" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
@@ -6083,16 +6078,16 @@
         <v>594</v>
       </c>
       <c r="B85" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C85" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D85" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E85" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F85">
         <v>3</v>
@@ -6107,7 +6102,7 @@
         <v>36</v>
       </c>
       <c r="J85" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
@@ -6115,16 +6110,16 @@
         <v>594</v>
       </c>
       <c r="B86" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C86" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D86" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E86" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F86">
         <v>3</v>
@@ -6139,7 +6134,7 @@
         <v>7</v>
       </c>
       <c r="J86" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
@@ -6147,16 +6142,16 @@
         <v>594</v>
       </c>
       <c r="B87" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C87" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D87" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E87" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F87">
         <v>3</v>
@@ -6171,7 +6166,7 @@
         <v>7</v>
       </c>
       <c r="J87" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
@@ -6179,16 +6174,16 @@
         <v>594</v>
       </c>
       <c r="B88" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C88" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D88" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E88" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F88">
         <v>3</v>
@@ -6203,7 +6198,7 @@
         <v>7</v>
       </c>
       <c r="J88" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
@@ -6211,16 +6206,16 @@
         <v>594</v>
       </c>
       <c r="B89" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C89" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D89" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E89" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F89">
         <v>3</v>
@@ -6235,7 +6230,7 @@
         <v>7</v>
       </c>
       <c r="J89" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
@@ -6243,16 +6238,16 @@
         <v>594</v>
       </c>
       <c r="B90" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C90" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D90" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E90" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F90">
         <v>3</v>
@@ -6275,16 +6270,16 @@
         <v>589</v>
       </c>
       <c r="B91" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C91" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D91" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E91" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F91">
         <v>3</v>
@@ -6299,7 +6294,7 @@
         <v>7</v>
       </c>
       <c r="J91" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
@@ -6307,16 +6302,16 @@
         <v>589</v>
       </c>
       <c r="B92" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C92" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D92" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E92" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F92">
         <v>3</v>
@@ -6331,7 +6326,7 @@
         <v>7</v>
       </c>
       <c r="J92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
@@ -6339,16 +6334,16 @@
         <v>589</v>
       </c>
       <c r="B93" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C93" t="s">
+        <v>938</v>
+      </c>
+      <c r="D93" t="s">
         <v>939</v>
       </c>
-      <c r="D93" t="s">
-        <v>940</v>
-      </c>
       <c r="E93" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F93">
         <v>3</v>
@@ -6363,7 +6358,7 @@
         <v>36</v>
       </c>
       <c r="J93" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
   </sheetData>
@@ -6377,6 +6372,7 @@
   <dimension ref="A1:J93"/>
   <sheetFormatPr defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="10" max="10" width="33.921875" customWidth="1"/>
   </cols>
@@ -6392,7 +6388,7 @@
         <v>123</v>
       </c>
       <c r="D1" t="s">
-        <v>701</v>
+        <v>124</v>
       </c>
       <c r="E1" t="s">
         <v>126</v>
@@ -6421,13 +6417,13 @@
         <v>694</v>
       </c>
       <c r="C2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -6453,13 +6449,13 @@
         <v>694</v>
       </c>
       <c r="C3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -6485,13 +6481,13 @@
         <v>694</v>
       </c>
       <c r="C4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E4" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -6517,13 +6513,13 @@
         <v>694</v>
       </c>
       <c r="C5" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D5" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E5" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -6549,13 +6545,13 @@
         <v>694</v>
       </c>
       <c r="C6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D6" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -6581,13 +6577,13 @@
         <v>694</v>
       </c>
       <c r="C7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -6613,13 +6609,13 @@
         <v>694</v>
       </c>
       <c r="C8" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -6645,13 +6641,13 @@
         <v>694</v>
       </c>
       <c r="C9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D9" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E9" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -6677,13 +6673,13 @@
         <v>694</v>
       </c>
       <c r="C10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -6709,13 +6705,13 @@
         <v>694</v>
       </c>
       <c r="C11" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -6741,13 +6737,13 @@
         <v>692</v>
       </c>
       <c r="C12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D12" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -6773,13 +6769,13 @@
         <v>690</v>
       </c>
       <c r="C13" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E13" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -6805,13 +6801,13 @@
         <v>690</v>
       </c>
       <c r="C14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D14" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E14" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -6837,13 +6833,13 @@
         <v>688</v>
       </c>
       <c r="C15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E15" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -6869,13 +6865,13 @@
         <v>688</v>
       </c>
       <c r="C16" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D16" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E16" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -6901,13 +6897,13 @@
         <v>685</v>
       </c>
       <c r="C17" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D17" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E17" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -6933,13 +6929,13 @@
         <v>685</v>
       </c>
       <c r="C18" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D18" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E18" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F18">
         <v>3</v>
@@ -6965,13 +6961,13 @@
         <v>681</v>
       </c>
       <c r="C19" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D19" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E19" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -6997,13 +6993,13 @@
         <v>681</v>
       </c>
       <c r="C20" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D20" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E20" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -7029,13 +7025,13 @@
         <v>681</v>
       </c>
       <c r="C21" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D21" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E21" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F21">
         <v>3</v>
@@ -7061,13 +7057,13 @@
         <v>679</v>
       </c>
       <c r="C22" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D22" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E22" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F22">
         <v>3</v>
@@ -7093,13 +7089,13 @@
         <v>678</v>
       </c>
       <c r="C23" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D23" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E23" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -7125,13 +7121,13 @@
         <v>678</v>
       </c>
       <c r="C24" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D24" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E24" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -7157,13 +7153,13 @@
         <v>675</v>
       </c>
       <c r="C25" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D25" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E25" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -7189,13 +7185,13 @@
         <v>675</v>
       </c>
       <c r="C26" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D26" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E26" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F26">
         <v>3</v>
@@ -7221,13 +7217,13 @@
         <v>675</v>
       </c>
       <c r="C27" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D27" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E27" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -7253,13 +7249,13 @@
         <v>673</v>
       </c>
       <c r="C28" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D28" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E28" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -7285,13 +7281,13 @@
         <v>673</v>
       </c>
       <c r="C29" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D29" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E29" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F29">
         <v>3</v>
@@ -7317,13 +7313,13 @@
         <v>672</v>
       </c>
       <c r="C30" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D30" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E30" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F30">
         <v>3</v>
@@ -7349,13 +7345,13 @@
         <v>671</v>
       </c>
       <c r="C31" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D31" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E31" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -7381,13 +7377,13 @@
         <v>671</v>
       </c>
       <c r="C32" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D32" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E32" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -7413,13 +7409,13 @@
         <v>670</v>
       </c>
       <c r="C33" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D33" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E33" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F33">
         <v>3</v>
@@ -7445,13 +7441,13 @@
         <v>670</v>
       </c>
       <c r="C34" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D34" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E34" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F34">
         <v>3</v>
@@ -7477,13 +7473,13 @@
         <v>669</v>
       </c>
       <c r="C35" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D35" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E35" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -7509,13 +7505,13 @@
         <v>669</v>
       </c>
       <c r="C36" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D36" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E36" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F36">
         <v>3</v>
@@ -7541,13 +7537,13 @@
         <v>666</v>
       </c>
       <c r="C37" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D37" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E37" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F37">
         <v>3</v>
@@ -7573,13 +7569,13 @@
         <v>664</v>
       </c>
       <c r="C38" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D38" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E38" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -7605,13 +7601,13 @@
         <v>664</v>
       </c>
       <c r="C39" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D39" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E39" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -7637,13 +7633,13 @@
         <v>662</v>
       </c>
       <c r="C40" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D40" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E40" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -7669,13 +7665,13 @@
         <v>660</v>
       </c>
       <c r="C41" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D41" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E41" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -7701,13 +7697,13 @@
         <v>660</v>
       </c>
       <c r="C42" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D42" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E42" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F42">
         <v>3</v>
@@ -7733,13 +7729,13 @@
         <v>658</v>
       </c>
       <c r="C43" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D43" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E43" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F43">
         <v>3</v>
@@ -7765,13 +7761,13 @@
         <v>656</v>
       </c>
       <c r="C44" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D44" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E44" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F44">
         <v>3</v>
@@ -7797,13 +7793,13 @@
         <v>654</v>
       </c>
       <c r="C45" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D45" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E45" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -7829,13 +7825,13 @@
         <v>652</v>
       </c>
       <c r="C46" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D46" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E46" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -7861,13 +7857,13 @@
         <v>651</v>
       </c>
       <c r="C47" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D47" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E47" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F47">
         <v>2</v>
@@ -7893,13 +7889,13 @@
         <v>651</v>
       </c>
       <c r="C48" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D48" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E48" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F48">
         <v>2</v>
@@ -7925,13 +7921,13 @@
         <v>651</v>
       </c>
       <c r="C49" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D49" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E49" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -7957,13 +7953,13 @@
         <v>650</v>
       </c>
       <c r="C50" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D50" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E50" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F50">
         <v>3</v>
@@ -7989,13 +7985,13 @@
         <v>648</v>
       </c>
       <c r="C51" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D51" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E51" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F51">
         <v>3</v>
@@ -8021,13 +8017,13 @@
         <v>647</v>
       </c>
       <c r="C52" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D52" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E52" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F52">
         <v>3</v>
@@ -8053,13 +8049,13 @@
         <v>645</v>
       </c>
       <c r="C53" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D53" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E53" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F53">
         <v>3</v>
@@ -8085,13 +8081,13 @@
         <v>644</v>
       </c>
       <c r="C54" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D54" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E54" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F54">
         <v>3</v>
@@ -8117,13 +8113,13 @@
         <v>641</v>
       </c>
       <c r="C55" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D55" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E55" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F55">
         <v>2</v>
@@ -8149,13 +8145,13 @@
         <v>639</v>
       </c>
       <c r="C56" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D56" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E56" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F56">
         <v>3</v>
@@ -8181,13 +8177,13 @@
         <v>637</v>
       </c>
       <c r="C57" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D57" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E57" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F57">
         <v>3</v>
@@ -8213,13 +8209,13 @@
         <v>635</v>
       </c>
       <c r="C58" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D58" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E58" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F58">
         <v>3</v>
@@ -8245,13 +8241,13 @@
         <v>634</v>
       </c>
       <c r="C59" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D59" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E59" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -8277,13 +8273,13 @@
         <v>633</v>
       </c>
       <c r="C60" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D60" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E60" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F60">
         <v>3</v>
@@ -8309,13 +8305,13 @@
         <v>631</v>
       </c>
       <c r="C61" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D61" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E61" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F61">
         <v>2</v>
@@ -8341,13 +8337,13 @@
         <v>629</v>
       </c>
       <c r="C62" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D62" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E62" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F62">
         <v>3</v>
@@ -8373,13 +8369,13 @@
         <v>627</v>
       </c>
       <c r="C63" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D63" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E63" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F63">
         <v>2</v>
@@ -8405,13 +8401,13 @@
         <v>623</v>
       </c>
       <c r="C64" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D64" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E64" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F64">
         <v>2</v>
@@ -8437,13 +8433,13 @@
         <v>623</v>
       </c>
       <c r="C65" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D65" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E65" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -8469,13 +8465,13 @@
         <v>623</v>
       </c>
       <c r="C66" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D66" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E66" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F66">
         <v>2</v>
@@ -8501,13 +8497,13 @@
         <v>623</v>
       </c>
       <c r="C67" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D67" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E67" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -8533,13 +8529,13 @@
         <v>623</v>
       </c>
       <c r="C68" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D68" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E68" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F68">
         <v>2</v>
@@ -8565,13 +8561,13 @@
         <v>623</v>
       </c>
       <c r="C69" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D69" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E69" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F69">
         <v>2</v>
@@ -8597,13 +8593,13 @@
         <v>623</v>
       </c>
       <c r="C70" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D70" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E70" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F70">
         <v>2</v>
@@ -8629,13 +8625,13 @@
         <v>621</v>
       </c>
       <c r="C71" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D71" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E71" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F71">
         <v>3</v>
@@ -8661,13 +8657,13 @@
         <v>619</v>
       </c>
       <c r="C72" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D72" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E72" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F72">
         <v>3</v>
@@ -8693,13 +8689,13 @@
         <v>618</v>
       </c>
       <c r="C73" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D73" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E73" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F73">
         <v>3</v>
@@ -8725,13 +8721,13 @@
         <v>616</v>
       </c>
       <c r="C74" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D74" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E74" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F74">
         <v>3</v>
@@ -8757,13 +8753,13 @@
         <v>614</v>
       </c>
       <c r="C75" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D75" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E75" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F75">
         <v>3</v>
@@ -8789,13 +8785,13 @@
         <v>612</v>
       </c>
       <c r="C76" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D76" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E76" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -8821,13 +8817,13 @@
         <v>612</v>
       </c>
       <c r="C77" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D77" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E77" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F77">
         <v>2</v>
@@ -8853,13 +8849,13 @@
         <v>612</v>
       </c>
       <c r="C78" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D78" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E78" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F78">
         <v>2</v>
@@ -8885,13 +8881,13 @@
         <v>612</v>
       </c>
       <c r="C79" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D79" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E79" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F79">
         <v>2</v>
@@ -8917,13 +8913,13 @@
         <v>610</v>
       </c>
       <c r="C80" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D80" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E80" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F80">
         <v>3</v>
@@ -8949,13 +8945,13 @@
         <v>607</v>
       </c>
       <c r="C81" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D81" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E81" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F81">
         <v>3</v>
@@ -8981,13 +8977,13 @@
         <v>606</v>
       </c>
       <c r="C82" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E82" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F82">
         <v>3</v>
@@ -9013,13 +9009,13 @@
         <v>603</v>
       </c>
       <c r="C83" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D83" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E83" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F83">
         <v>3</v>
@@ -9045,13 +9041,13 @@
         <v>603</v>
       </c>
       <c r="C84" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D84" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E84" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F84">
         <v>3</v>
@@ -9077,13 +9073,13 @@
         <v>601</v>
       </c>
       <c r="C85" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D85" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E85" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F85">
         <v>3</v>
@@ -9109,13 +9105,13 @@
         <v>601</v>
       </c>
       <c r="C86" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D86" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E86" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F86">
         <v>3</v>
@@ -9141,13 +9137,13 @@
         <v>596</v>
       </c>
       <c r="C87" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D87" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E87" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F87">
         <v>3</v>
@@ -9173,13 +9169,13 @@
         <v>596</v>
       </c>
       <c r="C88" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D88" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E88" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F88">
         <v>3</v>
@@ -9205,13 +9201,13 @@
         <v>596</v>
       </c>
       <c r="C89" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D89" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E89" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F89">
         <v>3</v>
@@ -9237,13 +9233,13 @@
         <v>593</v>
       </c>
       <c r="C90" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D90" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E90" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F90">
         <v>3</v>
@@ -9269,13 +9265,13 @@
         <v>593</v>
       </c>
       <c r="C91" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D91" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E91" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F91">
         <v>3</v>
@@ -9301,13 +9297,13 @@
         <v>591</v>
       </c>
       <c r="C92" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D92" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E92" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F92">
         <v>3</v>
@@ -9333,13 +9329,13 @@
         <v>588</v>
       </c>
       <c r="C93" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D93" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E93" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F93">
         <v>3</v>

--- a/데이터/opened_course2025_2.xlsx
+++ b/데이터/opened_course2025_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070B0A6A-F6F0-433E-B146-D8ACAF39E279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D636966D-7DEC-48E8-AA0F-AAD2D7F4C54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3382,6 +3382,7 @@
   <dimension ref="A1:J93"/>
   <sheetFormatPr defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="18.921875" customWidth="1"/>
     <col min="3" max="3" width="26.765625" customWidth="1"/>
   </cols>
   <sheetData>
